--- a/hall/resources/sample/BuildingFloor.xlsx
+++ b/hall/resources/sample/BuildingFloor.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingFloor" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="50">
   <si>
     <t>id</t>
   </si>
@@ -173,13 +173,25 @@
     <t>1_1</t>
   </si>
   <si>
-    <t>DC_BG_001.png</t>
+    <t>wddc_lc_8.png</t>
   </si>
   <si>
     <t>大厅</t>
   </si>
   <si>
-    <t>DC_BG_002.png</t>
+    <t>wddc_lc_5.png</t>
+  </si>
+  <si>
+    <t>10500_10400</t>
+  </si>
+  <si>
+    <t>吧台区</t>
+  </si>
+  <si>
+    <t>休息区</t>
+  </si>
+  <si>
+    <t>wddc_lc_6.png</t>
   </si>
   <si>
     <t>10600_10600</t>
@@ -188,16 +200,7 @@
     <t>提款机</t>
   </si>
   <si>
-    <t>10500_10400</t>
-  </si>
-  <si>
-    <t>吧台区</t>
-  </si>
-  <si>
-    <t>休息区</t>
-  </si>
-  <si>
-    <t>DC_BG_003.png</t>
+    <t>wddc_lc_3.png</t>
   </si>
   <si>
     <t>10100_10100_10100_10100</t>
@@ -206,7 +209,7 @@
     <t>slot机台</t>
   </si>
   <si>
-    <t>DC_BG_004.png</t>
+    <t>wddc_lc_4.png</t>
   </si>
   <si>
     <t>10200_10200</t>
@@ -215,7 +218,7 @@
     <t>扑克牌桌</t>
   </si>
   <si>
-    <t>DC_BG_005.png</t>
+    <t>wddc_lc_2.png</t>
   </si>
   <si>
     <t>幸运转盘</t>
@@ -1824,7 +1827,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.375" customWidth="1"/>
@@ -1972,16 +1975,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="1">
-        <v>6</v>
+        <f>_xlfn.XLOOKUP(H6,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
+        <v>4</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="1">
-        <v>6</v>
+        <f>_xlfn.XLOOKUP(J6,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
+        <v>5</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1991,7 +1996,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:15">
+    <row r="7" customHeight="1" spans="1:22">
       <c r="A7">
         <f t="shared" ref="A7:A12" si="0">B7*1000+C7</f>
         <v>1002</v>
@@ -2006,24 +2011,22 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G7" s="1">
-        <f>_xlfn.XLOOKUP(H7,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I7" s="1">
-        <f>_xlfn.XLOOKUP(J7,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -2032,6 +2035,7 @@
       <c r="O7">
         <v>180</v>
       </c>
+      <c r="V7" s="1"/>
     </row>
     <row r="8" customHeight="1" spans="1:15">
       <c r="A8">
@@ -2048,38 +2052,38 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G8" s="1">
         <f>_xlfn.XLOOKUP(H8,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I8" s="1">
         <f>_xlfn.XLOOKUP(J8,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" s="1">
         <f>_xlfn.XLOOKUP(L8,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M8" s="1">
         <f>_xlfn.XLOOKUP(N8,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O8">
         <v>180</v>
@@ -2100,24 +2104,24 @@
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G9" s="1">
         <f>_xlfn.XLOOKUP(H9,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>2</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" s="1">
         <f>_xlfn.XLOOKUP(J9,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>2</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -2142,7 +2146,7 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" s="3">
         <v>10300</v>
@@ -2152,7 +2156,7 @@
         <v>3</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -2179,38 +2183,38 @@
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G11" s="1">
         <f>_xlfn.XLOOKUP(H11,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I11" s="1">
         <f>_xlfn.XLOOKUP(J11,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K11" s="1">
         <f>_xlfn.XLOOKUP(L11,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M11" s="1">
         <f>_xlfn.XLOOKUP(N11,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O11">
         <v>180</v>
@@ -2231,24 +2235,24 @@
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G12" s="1">
         <f>_xlfn.XLOOKUP(H12,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>2</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I12" s="1">
         <f>_xlfn.XLOOKUP(J12,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>2</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -2273,7 +2277,7 @@
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F13" s="3">
         <v>10300</v>
@@ -2283,7 +2287,7 @@
         <v>3</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -2310,38 +2314,38 @@
         <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1">
         <f>_xlfn.XLOOKUP(H14,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I14" s="1">
         <f>_xlfn.XLOOKUP(J14,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K14" s="1">
         <f>_xlfn.XLOOKUP(L14,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M14" s="1">
         <f>_xlfn.XLOOKUP(N14,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O14">
         <v>180</v>
@@ -2359,27 +2363,27 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" s="1">
         <f>_xlfn.XLOOKUP(H15,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>2</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15" s="1">
         <f>_xlfn.XLOOKUP(J15,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>2</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -2401,10 +2405,10 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F16" s="3">
         <v>10300</v>
@@ -2414,7 +2418,7 @@
         <v>3</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -2438,41 +2442,41 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" s="1">
         <f>_xlfn.XLOOKUP(H17,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I17" s="1">
         <f>_xlfn.XLOOKUP(J17,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K17" s="1">
         <f>_xlfn.XLOOKUP(L17,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M17" s="1">
         <f>_xlfn.XLOOKUP(N17,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O17">
         <v>180</v>
@@ -2490,27 +2494,27 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G18" s="1">
         <f>_xlfn.XLOOKUP(H18,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>2</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I18" s="1">
         <f>_xlfn.XLOOKUP(J18,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>2</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -2532,10 +2536,10 @@
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F19" s="3">
         <v>10300</v>
@@ -2545,7 +2549,7 @@
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -2569,41 +2573,41 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G20" s="1">
         <f>_xlfn.XLOOKUP(H20,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I20" s="1">
         <f>_xlfn.XLOOKUP(J20,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K20" s="1">
         <f>_xlfn.XLOOKUP(L20,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M20" s="1">
         <f>_xlfn.XLOOKUP(N20,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O20">
         <v>180</v>
@@ -2621,27 +2625,27 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G21" s="1">
         <f>_xlfn.XLOOKUP(H21,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>2</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="1">
         <f>_xlfn.XLOOKUP(J21,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>2</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -2663,10 +2667,10 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F22" s="3">
         <v>10300</v>
@@ -2676,7 +2680,7 @@
         <v>3</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -2700,41 +2704,41 @@
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G23" s="1">
         <f>_xlfn.XLOOKUP(H23,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I23" s="1">
         <f>_xlfn.XLOOKUP(J23,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K23" s="1">
         <f>_xlfn.XLOOKUP(L23,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M23" s="1">
         <f>_xlfn.XLOOKUP(N23,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>1</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O23">
         <v>180</v>
@@ -2752,27 +2756,27 @@
         <v>19</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G24" s="1">
         <f>_xlfn.XLOOKUP(H24,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>2</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="1">
         <f>_xlfn.XLOOKUP(J24,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
         <v>2</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -2794,10 +2798,10 @@
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F25" s="3">
         <v>10300</v>
@@ -2807,7 +2811,7 @@
         <v>3</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -2831,10 +2835,10 @@
         <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F26" s="3">
         <v>10700</v>
@@ -2844,7 +2848,7 @@
         <v>7</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I26" s="1"/>
       <c r="O26">

--- a/hall/resources/sample/BuildingFloor.xlsx
+++ b/hall/resources/sample/BuildingFloor.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingFloor" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -257,7 +258,7 @@
     <t>1_110</t>
   </si>
   <si>
-    <t>1_120</t>
+    <t>1_999</t>
   </si>
   <si>
     <t>DC_BG_006.png</t>
@@ -1549,6 +1550,582 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="BuildingFunction"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>建筑类型</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>#备注</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="B2" t="str">
+            <v>int</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>typeID</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5">
+            <v>1</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>slot机台</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6">
+            <v>1</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>slot机台</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>1</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>slot机台</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8">
+            <v>1</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>slot机台</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9">
+            <v>1</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>slot机台</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10">
+            <v>1</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>slot机台</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11">
+            <v>1</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>slot机台</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12">
+            <v>1</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>slot机台</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13">
+            <v>1</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>slot机台</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14">
+            <v>1</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>slot机台</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15">
+            <v>1</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>slot机台</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16">
+            <v>2</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>扑克牌桌</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17">
+            <v>2</v>
+          </cell>
+          <cell r="C17" t="str">
+            <v>扑克牌桌</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18">
+            <v>2</v>
+          </cell>
+          <cell r="C18" t="str">
+            <v>扑克牌桌</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19">
+            <v>2</v>
+          </cell>
+          <cell r="C19" t="str">
+            <v>扑克牌桌</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20">
+            <v>2</v>
+          </cell>
+          <cell r="C20" t="str">
+            <v>扑克牌桌</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21">
+            <v>2</v>
+          </cell>
+          <cell r="C21" t="str">
+            <v>扑克牌桌</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22">
+            <v>2</v>
+          </cell>
+          <cell r="C22" t="str">
+            <v>扑克牌桌</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23">
+            <v>2</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>扑克牌桌</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24">
+            <v>2</v>
+          </cell>
+          <cell r="C24" t="str">
+            <v>扑克牌桌</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25">
+            <v>2</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>扑克牌桌</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26">
+            <v>2</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>扑克牌桌</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27">
+            <v>3</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>幸运转盘</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28">
+            <v>3</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>幸运转盘</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29">
+            <v>3</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>幸运转盘</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30">
+            <v>3</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>幸运转盘</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31">
+            <v>3</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>幸运转盘</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32">
+            <v>3</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>幸运转盘</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33">
+            <v>3</v>
+          </cell>
+          <cell r="C33" t="str">
+            <v>幸运转盘</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34">
+            <v>3</v>
+          </cell>
+          <cell r="C34" t="str">
+            <v>幸运转盘</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35">
+            <v>3</v>
+          </cell>
+          <cell r="C35" t="str">
+            <v>幸运转盘</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36">
+            <v>3</v>
+          </cell>
+          <cell r="C36" t="str">
+            <v>幸运转盘</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37">
+            <v>3</v>
+          </cell>
+          <cell r="C37" t="str">
+            <v>幸运转盘</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38">
+            <v>4</v>
+          </cell>
+          <cell r="C38" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39">
+            <v>4</v>
+          </cell>
+          <cell r="C39" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40">
+            <v>4</v>
+          </cell>
+          <cell r="C40" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41">
+            <v>4</v>
+          </cell>
+          <cell r="C41" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42">
+            <v>4</v>
+          </cell>
+          <cell r="C42" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="B43">
+            <v>4</v>
+          </cell>
+          <cell r="C43" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="B44">
+            <v>4</v>
+          </cell>
+          <cell r="C44" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="B45">
+            <v>4</v>
+          </cell>
+          <cell r="C45" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="B46">
+            <v>4</v>
+          </cell>
+          <cell r="C46" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="B47">
+            <v>4</v>
+          </cell>
+          <cell r="C47" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="B48">
+            <v>4</v>
+          </cell>
+          <cell r="C48" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="B49">
+            <v>5</v>
+          </cell>
+          <cell r="C49" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="B50">
+            <v>5</v>
+          </cell>
+          <cell r="C50" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="B51">
+            <v>5</v>
+          </cell>
+          <cell r="C51" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="B52">
+            <v>5</v>
+          </cell>
+          <cell r="C52" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="B53">
+            <v>5</v>
+          </cell>
+          <cell r="C53" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="B54">
+            <v>5</v>
+          </cell>
+          <cell r="C54" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="B55">
+            <v>5</v>
+          </cell>
+          <cell r="C55" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="B56">
+            <v>5</v>
+          </cell>
+          <cell r="C56" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="B57">
+            <v>5</v>
+          </cell>
+          <cell r="C57" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="B58">
+            <v>5</v>
+          </cell>
+          <cell r="C58" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="B59">
+            <v>5</v>
+          </cell>
+          <cell r="C59" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="B60">
+            <v>6</v>
+          </cell>
+          <cell r="C60" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="B61">
+            <v>6</v>
+          </cell>
+          <cell r="C61" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="B62">
+            <v>6</v>
+          </cell>
+          <cell r="C62" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="B63">
+            <v>6</v>
+          </cell>
+          <cell r="C63" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="B64">
+            <v>6</v>
+          </cell>
+          <cell r="C64" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="B65">
+            <v>6</v>
+          </cell>
+          <cell r="C65" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="B66">
+            <v>6</v>
+          </cell>
+          <cell r="C66" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="B67">
+            <v>6</v>
+          </cell>
+          <cell r="C67" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="B68">
+            <v>6</v>
+          </cell>
+          <cell r="C68" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="B69">
+            <v>6</v>
+          </cell>
+          <cell r="C69" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="B70">
+            <v>6</v>
+          </cell>
+          <cell r="C70" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="B71">
+            <v>7</v>
+          </cell>
+          <cell r="C71" t="str">
+            <v>停机坪</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="B72">
+            <v>7</v>
+          </cell>
+          <cell r="C72" t="str">
+            <v>停机坪</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
@@ -2823,7 +3400,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:15">
+    <row r="26" customFormat="1" customHeight="1" spans="1:15">
       <c r="A26">
         <f t="shared" si="1"/>
         <v>1021</v>
@@ -2844,7 +3421,7 @@
         <v>10700</v>
       </c>
       <c r="G26" s="1">
-        <f>_xlfn.XLOOKUP(H26,[1]BuildingFunction!$C:$C,[1]BuildingFunction!$B:$B)</f>
+        <f>_xlfn.XLOOKUP(H26,[2]BuildingFunction!$C:$C,[2]BuildingFunction!$B:$B)</f>
         <v>7</v>
       </c>
       <c r="H26" s="4" t="s">

--- a/hall/resources/sample/BuildingFloor.xlsx
+++ b/hall/resources/sample/BuildingFloor.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingFloor" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="54">
   <si>
     <t>id</t>
   </si>
@@ -256,6 +256,18 @@
   </si>
   <si>
     <t>1_110</t>
+  </si>
+  <si>
+    <t>1_120</t>
+  </si>
+  <si>
+    <t>1_130</t>
+  </si>
+  <si>
+    <t>1_140</t>
+  </si>
+  <si>
+    <t>1_150</t>
   </si>
   <si>
     <t>1_999</t>
@@ -1090,82 +1102,82 @@
         </row>
         <row r="16">
           <cell r="B16">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="C16" t="str">
-            <v>扑克牌桌</v>
+            <v>slot机台</v>
           </cell>
         </row>
         <row r="17">
           <cell r="B17">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="C17" t="str">
-            <v>扑克牌桌</v>
+            <v>slot机台</v>
           </cell>
         </row>
         <row r="18">
           <cell r="B18">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="C18" t="str">
-            <v>扑克牌桌</v>
+            <v>slot机台</v>
           </cell>
         </row>
         <row r="19">
           <cell r="B19">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="C19" t="str">
-            <v>扑克牌桌</v>
+            <v>slot机台</v>
           </cell>
         </row>
         <row r="20">
           <cell r="B20">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="C20" t="str">
-            <v>扑克牌桌</v>
+            <v>slot机台</v>
           </cell>
         </row>
         <row r="21">
           <cell r="B21">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="C21" t="str">
-            <v>扑克牌桌</v>
+            <v>slot机台</v>
           </cell>
         </row>
         <row r="22">
           <cell r="B22">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="C22" t="str">
-            <v>扑克牌桌</v>
+            <v>slot机台</v>
           </cell>
         </row>
         <row r="23">
           <cell r="B23">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="C23" t="str">
-            <v>扑克牌桌</v>
+            <v>slot机台</v>
           </cell>
         </row>
         <row r="24">
           <cell r="B24">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="C24" t="str">
-            <v>扑克牌桌</v>
+            <v>slot机台</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="C25" t="str">
-            <v>扑克牌桌</v>
+            <v>slot机台</v>
           </cell>
         </row>
         <row r="26">
@@ -1178,369 +1190,849 @@
         </row>
         <row r="27">
           <cell r="B27">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="C27" t="str">
-            <v>幸运转盘</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="28">
           <cell r="B28">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="C28" t="str">
-            <v>幸运转盘</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="C29" t="str">
-            <v>幸运转盘</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="C30" t="str">
-            <v>幸运转盘</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="31">
           <cell r="B31">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="C31" t="str">
-            <v>幸运转盘</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="32">
           <cell r="B32">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="C32" t="str">
-            <v>幸运转盘</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="33">
           <cell r="B33">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="C33" t="str">
-            <v>幸运转盘</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="C34" t="str">
-            <v>幸运转盘</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="C35" t="str">
-            <v>幸运转盘</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="36">
           <cell r="B36">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="C36" t="str">
-            <v>幸运转盘</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="37">
           <cell r="B37">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="C37" t="str">
-            <v>幸运转盘</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="38">
           <cell r="B38">
-            <v>4</v>
+            <v>2</v>
           </cell>
           <cell r="C38" t="str">
-            <v>吧台区</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="39">
           <cell r="B39">
-            <v>4</v>
+            <v>2</v>
           </cell>
           <cell r="C39" t="str">
-            <v>吧台区</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="40">
           <cell r="B40">
-            <v>4</v>
+            <v>2</v>
           </cell>
           <cell r="C40" t="str">
-            <v>吧台区</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="41">
           <cell r="B41">
-            <v>4</v>
+            <v>2</v>
           </cell>
           <cell r="C41" t="str">
-            <v>吧台区</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="42">
           <cell r="B42">
-            <v>4</v>
+            <v>2</v>
           </cell>
           <cell r="C42" t="str">
-            <v>吧台区</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="43">
           <cell r="B43">
-            <v>4</v>
+            <v>2</v>
           </cell>
           <cell r="C43" t="str">
-            <v>吧台区</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="44">
           <cell r="B44">
-            <v>4</v>
+            <v>2</v>
           </cell>
           <cell r="C44" t="str">
-            <v>吧台区</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="45">
           <cell r="B45">
-            <v>4</v>
+            <v>2</v>
           </cell>
           <cell r="C45" t="str">
-            <v>吧台区</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="46">
           <cell r="B46">
-            <v>4</v>
+            <v>2</v>
           </cell>
           <cell r="C46" t="str">
-            <v>吧台区</v>
+            <v>扑克牌桌</v>
           </cell>
         </row>
         <row r="47">
           <cell r="B47">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="C47" t="str">
-            <v>吧台区</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="48">
           <cell r="B48">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="C48" t="str">
-            <v>吧台区</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="49">
           <cell r="B49">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="C49" t="str">
-            <v>休息区</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="50">
           <cell r="B50">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="C50" t="str">
-            <v>休息区</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="51">
           <cell r="B51">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="C51" t="str">
-            <v>休息区</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="52">
           <cell r="B52">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="C52" t="str">
-            <v>休息区</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="53">
           <cell r="B53">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="C53" t="str">
-            <v>休息区</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="54">
           <cell r="B54">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="C54" t="str">
-            <v>休息区</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="55">
           <cell r="B55">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="C55" t="str">
-            <v>休息区</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="56">
           <cell r="B56">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="C56" t="str">
-            <v>休息区</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="57">
           <cell r="B57">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="C57" t="str">
-            <v>休息区</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="58">
           <cell r="B58">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="C58" t="str">
-            <v>休息区</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="59">
           <cell r="B59">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="C59" t="str">
-            <v>休息区</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="60">
           <cell r="B60">
-            <v>6</v>
+            <v>3</v>
           </cell>
           <cell r="C60" t="str">
-            <v>提款机</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="61">
           <cell r="B61">
-            <v>6</v>
+            <v>3</v>
           </cell>
           <cell r="C61" t="str">
-            <v>提款机</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="62">
           <cell r="B62">
-            <v>6</v>
+            <v>3</v>
           </cell>
           <cell r="C62" t="str">
-            <v>提款机</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="63">
           <cell r="B63">
-            <v>6</v>
+            <v>3</v>
           </cell>
           <cell r="C63" t="str">
-            <v>提款机</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="64">
           <cell r="B64">
-            <v>6</v>
+            <v>3</v>
           </cell>
           <cell r="C64" t="str">
-            <v>提款机</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="65">
           <cell r="B65">
-            <v>6</v>
+            <v>3</v>
           </cell>
           <cell r="C65" t="str">
-            <v>提款机</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="66">
           <cell r="B66">
-            <v>6</v>
+            <v>3</v>
           </cell>
           <cell r="C66" t="str">
-            <v>提款机</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="67">
           <cell r="B67">
-            <v>6</v>
+            <v>3</v>
           </cell>
           <cell r="C67" t="str">
-            <v>提款机</v>
+            <v>幸运转盘</v>
           </cell>
         </row>
         <row r="68">
           <cell r="B68">
-            <v>6</v>
+            <v>4</v>
           </cell>
           <cell r="C68" t="str">
-            <v>提款机</v>
+            <v>吧台区</v>
           </cell>
         </row>
         <row r="69">
           <cell r="B69">
-            <v>6</v>
+            <v>4</v>
           </cell>
           <cell r="C69" t="str">
-            <v>提款机</v>
+            <v>吧台区</v>
           </cell>
         </row>
         <row r="70">
           <cell r="B70">
-            <v>6</v>
+            <v>4</v>
           </cell>
           <cell r="C70" t="str">
-            <v>提款机</v>
+            <v>吧台区</v>
           </cell>
         </row>
         <row r="71">
           <cell r="B71">
-            <v>7</v>
+            <v>4</v>
           </cell>
           <cell r="C71" t="str">
-            <v>停机坪</v>
+            <v>吧台区</v>
           </cell>
         </row>
         <row r="72">
           <cell r="B72">
+            <v>4</v>
+          </cell>
+          <cell r="C72" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="B73">
+            <v>4</v>
+          </cell>
+          <cell r="C73" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="B74">
+            <v>4</v>
+          </cell>
+          <cell r="C74" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="B75">
+            <v>4</v>
+          </cell>
+          <cell r="C75" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="B76">
+            <v>4</v>
+          </cell>
+          <cell r="C76" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="B77">
+            <v>4</v>
+          </cell>
+          <cell r="C77" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="B78">
+            <v>4</v>
+          </cell>
+          <cell r="C78" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="B79">
+            <v>4</v>
+          </cell>
+          <cell r="C79" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="B80">
+            <v>4</v>
+          </cell>
+          <cell r="C80" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="B81">
+            <v>4</v>
+          </cell>
+          <cell r="C81" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="B82">
+            <v>4</v>
+          </cell>
+          <cell r="C82" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="B83">
+            <v>4</v>
+          </cell>
+          <cell r="C83" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="B84">
+            <v>4</v>
+          </cell>
+          <cell r="C84" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="B85">
+            <v>4</v>
+          </cell>
+          <cell r="C85" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="B86">
+            <v>4</v>
+          </cell>
+          <cell r="C86" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="B87">
+            <v>4</v>
+          </cell>
+          <cell r="C87" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="B88">
+            <v>4</v>
+          </cell>
+          <cell r="C88" t="str">
+            <v>吧台区</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="B89">
+            <v>5</v>
+          </cell>
+          <cell r="C89" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="B90">
+            <v>5</v>
+          </cell>
+          <cell r="C90" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="B91">
+            <v>5</v>
+          </cell>
+          <cell r="C91" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="B92">
+            <v>5</v>
+          </cell>
+          <cell r="C92" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="B93">
+            <v>5</v>
+          </cell>
+          <cell r="C93" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="B94">
+            <v>5</v>
+          </cell>
+          <cell r="C94" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="B95">
+            <v>5</v>
+          </cell>
+          <cell r="C95" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="B96">
+            <v>5</v>
+          </cell>
+          <cell r="C96" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="B97">
+            <v>5</v>
+          </cell>
+          <cell r="C97" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="B98">
+            <v>5</v>
+          </cell>
+          <cell r="C98" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="B99">
+            <v>5</v>
+          </cell>
+          <cell r="C99" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="B100">
+            <v>5</v>
+          </cell>
+          <cell r="C100" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="B101">
+            <v>5</v>
+          </cell>
+          <cell r="C101" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="B102">
+            <v>5</v>
+          </cell>
+          <cell r="C102" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="B103">
+            <v>5</v>
+          </cell>
+          <cell r="C103" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="B104">
+            <v>5</v>
+          </cell>
+          <cell r="C104" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="B105">
+            <v>5</v>
+          </cell>
+          <cell r="C105" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="B106">
+            <v>5</v>
+          </cell>
+          <cell r="C106" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="B107">
+            <v>5</v>
+          </cell>
+          <cell r="C107" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="B108">
+            <v>5</v>
+          </cell>
+          <cell r="C108" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="B109">
+            <v>5</v>
+          </cell>
+          <cell r="C109" t="str">
+            <v>休息区</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="B110">
+            <v>6</v>
+          </cell>
+          <cell r="C110" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="B111">
+            <v>6</v>
+          </cell>
+          <cell r="C111" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="B112">
+            <v>6</v>
+          </cell>
+          <cell r="C112" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="B113">
+            <v>6</v>
+          </cell>
+          <cell r="C113" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="B114">
+            <v>6</v>
+          </cell>
+          <cell r="C114" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="B115">
+            <v>6</v>
+          </cell>
+          <cell r="C115" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="B116">
+            <v>6</v>
+          </cell>
+          <cell r="C116" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="B117">
+            <v>6</v>
+          </cell>
+          <cell r="C117" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="B118">
+            <v>6</v>
+          </cell>
+          <cell r="C118" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="B119">
+            <v>6</v>
+          </cell>
+          <cell r="C119" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="B120">
+            <v>6</v>
+          </cell>
+          <cell r="C120" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="B121">
+            <v>6</v>
+          </cell>
+          <cell r="C121" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="B122">
+            <v>6</v>
+          </cell>
+          <cell r="C122" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="B123">
+            <v>6</v>
+          </cell>
+          <cell r="C123" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="B124">
+            <v>6</v>
+          </cell>
+          <cell r="C124" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="B125">
+            <v>6</v>
+          </cell>
+          <cell r="C125" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="B126">
+            <v>6</v>
+          </cell>
+          <cell r="C126" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="B127">
+            <v>6</v>
+          </cell>
+          <cell r="C127" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="B128">
+            <v>6</v>
+          </cell>
+          <cell r="C128" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="B129">
+            <v>6</v>
+          </cell>
+          <cell r="C129" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="B130">
+            <v>6</v>
+          </cell>
+          <cell r="C130" t="str">
+            <v>提款机</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="B131">
             <v>7</v>
           </cell>
-          <cell r="C72" t="str">
+          <cell r="C131" t="str">
+            <v>停机坪</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="B132">
+            <v>7</v>
+          </cell>
+          <cell r="C132" t="str">
             <v>停机坪</v>
           </cell>
         </row>
@@ -2404,7 +2896,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.375" customWidth="1"/>
@@ -2528,7 +3020,7 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5">
-        <v>180</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:15">
@@ -2570,7 +3062,7 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6">
-        <v>180</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:22">
@@ -2610,7 +3102,7 @@
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="V7" s="1"/>
     </row>
@@ -2663,10 +3155,10 @@
         <v>30</v>
       </c>
       <c r="O8">
-        <v>180</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:15">
+    <row r="9" customHeight="1" spans="1:17">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>1004</v>
@@ -2705,10 +3197,11 @@
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9">
-        <v>180</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Q9" s="4"/>
     </row>
-    <row r="10" customHeight="1" spans="1:15">
+    <row r="10" customHeight="1" spans="1:17">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>1005</v>
@@ -2744,8 +3237,9 @@
       <c r="O10">
         <v>180</v>
       </c>
+      <c r="Q10" s="4"/>
     </row>
-    <row r="11" customHeight="1" spans="1:15">
+    <row r="11" customHeight="1" spans="1:17">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>1006</v>
@@ -2757,7 +3251,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -2794,10 +3288,11 @@
         <v>30</v>
       </c>
       <c r="O11">
-        <v>180</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="Q11" s="4"/>
     </row>
-    <row r="12" customHeight="1" spans="1:15">
+    <row r="12" customHeight="1" spans="1:17">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>1007</v>
@@ -2809,7 +3304,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s">
         <v>31</v>
@@ -2836,10 +3331,11 @@
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12">
-        <v>180</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="Q12" s="4"/>
     </row>
-    <row r="13" customHeight="1" spans="1:15">
+    <row r="13" customHeight="1" spans="1:17">
       <c r="A13">
         <f t="shared" ref="A13:A26" si="1">B13*1000+C13</f>
         <v>1008</v>
@@ -2851,7 +3347,7 @@
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>34</v>
@@ -2873,10 +3369,11 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13">
-        <v>180</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="Q13" s="4"/>
     </row>
-    <row r="14" customHeight="1" spans="1:15">
+    <row r="14" customHeight="1" spans="1:17">
       <c r="A14">
         <f t="shared" si="1"/>
         <v>1009</v>
@@ -2888,7 +3385,7 @@
         <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -2924,11 +3421,12 @@
       <c r="N14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O14">
-        <v>180</v>
-      </c>
+      <c r="O14" s="4">
+        <v>1500</v>
+      </c>
+      <c r="Q14" s="4"/>
     </row>
-    <row r="15" customHeight="1" spans="1:15">
+    <row r="15" customHeight="1" spans="1:17">
       <c r="A15">
         <f t="shared" si="1"/>
         <v>1010</v>
@@ -2940,7 +3438,7 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
         <v>31</v>
@@ -2966,11 +3464,12 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
-      <c r="O15">
-        <v>180</v>
-      </c>
+      <c r="O15" s="4">
+        <v>3600</v>
+      </c>
+      <c r="Q15" s="4"/>
     </row>
-    <row r="16" customHeight="1" spans="1:15">
+    <row r="16" customHeight="1" spans="1:17">
       <c r="A16">
         <f t="shared" si="1"/>
         <v>1011</v>
@@ -2982,7 +3481,7 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E16" t="s">
         <v>34</v>
@@ -3003,11 +3502,12 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
-      <c r="O16">
-        <v>180</v>
-      </c>
+      <c r="O16" s="4">
+        <v>4200</v>
+      </c>
+      <c r="Q16" s="4"/>
     </row>
-    <row r="17" customHeight="1" spans="1:15">
+    <row r="17" customHeight="1" spans="1:17">
       <c r="A17">
         <f t="shared" si="1"/>
         <v>1012</v>
@@ -3019,7 +3519,7 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -3055,11 +3555,12 @@
       <c r="N17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O17">
-        <v>180</v>
-      </c>
+      <c r="O17" s="4">
+        <v>12000</v>
+      </c>
+      <c r="Q17" s="4"/>
     </row>
-    <row r="18" customHeight="1" spans="1:15">
+    <row r="18" customHeight="1" spans="1:17">
       <c r="A18">
         <f t="shared" si="1"/>
         <v>1013</v>
@@ -3071,7 +3572,7 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
         <v>31</v>
@@ -3097,11 +3598,12 @@
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
-      <c r="O18">
-        <v>180</v>
-      </c>
+      <c r="O18" s="4">
+        <v>13200</v>
+      </c>
+      <c r="Q18" s="4"/>
     </row>
-    <row r="19" customHeight="1" spans="1:15">
+    <row r="19" customHeight="1" spans="1:17">
       <c r="A19">
         <f t="shared" si="1"/>
         <v>1014</v>
@@ -3113,7 +3615,7 @@
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
         <v>34</v>
@@ -3134,11 +3636,12 @@
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
-      <c r="O19">
-        <v>180</v>
-      </c>
+      <c r="O19" s="4">
+        <v>14400</v>
+      </c>
+      <c r="Q19" s="4"/>
     </row>
-    <row r="20" customHeight="1" spans="1:15">
+    <row r="20" customHeight="1" spans="1:17">
       <c r="A20">
         <f t="shared" si="1"/>
         <v>1015</v>
@@ -3150,7 +3653,7 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E20" t="s">
         <v>28</v>
@@ -3186,11 +3689,12 @@
       <c r="N20" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O20">
-        <v>180</v>
-      </c>
+      <c r="O20" s="4">
+        <v>33600</v>
+      </c>
+      <c r="Q20" s="4"/>
     </row>
-    <row r="21" customHeight="1" spans="1:15">
+    <row r="21" customHeight="1" spans="1:17">
       <c r="A21">
         <f t="shared" si="1"/>
         <v>1016</v>
@@ -3202,7 +3706,7 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E21" t="s">
         <v>31</v>
@@ -3228,11 +3732,12 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
-      <c r="O21">
-        <v>180</v>
-      </c>
+      <c r="O21" s="4">
+        <v>36000</v>
+      </c>
+      <c r="Q21" s="4"/>
     </row>
-    <row r="22" customHeight="1" spans="1:15">
+    <row r="22" customHeight="1" spans="1:17">
       <c r="A22">
         <f t="shared" si="1"/>
         <v>1017</v>
@@ -3244,7 +3749,7 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s">
         <v>34</v>
@@ -3265,11 +3770,12 @@
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
-      <c r="O22">
-        <v>180</v>
-      </c>
+      <c r="O22" s="4">
+        <v>38400</v>
+      </c>
+      <c r="Q22" s="4"/>
     </row>
-    <row r="23" customHeight="1" spans="1:15">
+    <row r="23" customHeight="1" spans="1:17">
       <c r="A23">
         <f t="shared" si="1"/>
         <v>1018</v>
@@ -3281,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
         <v>28</v>
@@ -3317,11 +3823,12 @@
       <c r="N23" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O23">
-        <v>180</v>
-      </c>
+      <c r="O23" s="4">
+        <v>81600</v>
+      </c>
+      <c r="Q23" s="4"/>
     </row>
-    <row r="24" customHeight="1" spans="1:15">
+    <row r="24" customHeight="1" spans="1:17">
       <c r="A24">
         <f t="shared" si="1"/>
         <v>1019</v>
@@ -3333,7 +3840,7 @@
         <v>19</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E24" t="s">
         <v>31</v>
@@ -3359,11 +3866,12 @@
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
-      <c r="O24">
-        <v>180</v>
-      </c>
+      <c r="O24" s="4">
+        <v>86400</v>
+      </c>
+      <c r="Q24" s="4"/>
     </row>
-    <row r="25" customHeight="1" spans="1:15">
+    <row r="25" customHeight="1" spans="1:17">
       <c r="A25">
         <f t="shared" si="1"/>
         <v>1020</v>
@@ -3375,7 +3883,7 @@
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E25" t="s">
         <v>34</v>
@@ -3396,11 +3904,12 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
-      <c r="O25">
-        <v>180</v>
-      </c>
+      <c r="O25" s="4">
+        <v>91200</v>
+      </c>
+      <c r="Q25" s="4"/>
     </row>
-    <row r="26" customFormat="1" customHeight="1" spans="1:15">
+    <row r="26" customFormat="1" customHeight="1" spans="1:17">
       <c r="A26">
         <f t="shared" si="1"/>
         <v>1021</v>
@@ -3412,10 +3921,10 @@
         <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E26" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F26" s="3">
         <v>10700</v>
@@ -3425,12 +3934,19 @@
         <v>7</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I26" s="1"/>
-      <c r="O26">
-        <v>180</v>
-      </c>
+      <c r="O26" s="4">
+        <v>91200</v>
+      </c>
+      <c r="Q26" s="4"/>
+    </row>
+    <row r="27" customHeight="1" spans="17:17">
+      <c r="Q27" s="4"/>
+    </row>
+    <row r="28" customHeight="1" spans="17:17">
+      <c r="Q28" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
